--- a/data/all_students.xlsx
+++ b/data/all_students.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,25 +446,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Caleb Bett</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>English</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Kiswahili</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Kiswahili</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
@@ -486,17 +481,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>80</v>
+      </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>54</v>
-      </c>
-      <c r="H2" t="n">
         <v>92</v>
       </c>
     </row>
@@ -516,17 +510,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>74</v>
+      </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>64</v>
-      </c>
-      <c r="H3" t="n">
         <v>54</v>
       </c>
     </row>
@@ -546,17 +539,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>94</v>
+      </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>66</v>
-      </c>
-      <c r="H4" t="n">
         <v>84</v>
       </c>
     </row>
@@ -576,17 +568,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>45</v>
+      </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>52</v>
-      </c>
-      <c r="H5" t="n">
         <v>48</v>
       </c>
     </row>
@@ -606,17 +597,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>85</v>
+      </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H6" t="n">
         <v>88</v>
       </c>
     </row>
@@ -636,17 +626,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>68</v>
+      </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>70</v>
-      </c>
-      <c r="H7" t="n">
         <v>65</v>
       </c>
     </row>
@@ -666,17 +655,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>55</v>
+      </c>
       <c r="E8" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>61</v>
-      </c>
-      <c r="H8" t="n">
         <v>50</v>
       </c>
     </row>
@@ -696,17 +684,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>92</v>
+      </c>
       <c r="E9" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>85</v>
-      </c>
-      <c r="H9" t="n">
         <v>95</v>
       </c>
     </row>
@@ -726,17 +713,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>41</v>
+      </c>
       <c r="E10" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
-      </c>
-      <c r="H10" t="n">
         <v>38</v>
       </c>
     </row>
@@ -756,17 +742,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>79</v>
+      </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G11" t="n">
-        <v>77</v>
-      </c>
-      <c r="H11" t="n">
         <v>83</v>
       </c>
     </row>
@@ -786,17 +771,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>63</v>
+      </c>
       <c r="E12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
-      </c>
-      <c r="H12" t="n">
         <v>72</v>
       </c>
     </row>
@@ -816,17 +800,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>87</v>
+      </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F13" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G13" t="n">
-        <v>89</v>
-      </c>
-      <c r="H13" t="n">
         <v>91</v>
       </c>
     </row>
@@ -846,17 +829,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>70</v>
+      </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G14" t="n">
-        <v>73</v>
-      </c>
-      <c r="H14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -876,17 +858,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>58</v>
+      </c>
       <c r="E15" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
-      </c>
-      <c r="H15" t="n">
         <v>59</v>
       </c>
     </row>
@@ -906,17 +887,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>76</v>
+      </c>
       <c r="E16" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>82</v>
-      </c>
-      <c r="H16" t="n">
         <v>78</v>
       </c>
     </row>
@@ -936,17 +916,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>89</v>
+      </c>
       <c r="E17" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F17" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G17" t="n">
-        <v>87</v>
-      </c>
-      <c r="H17" t="n">
         <v>93</v>
       </c>
     </row>
@@ -966,17 +945,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>47</v>
+      </c>
       <c r="E18" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
-      </c>
-      <c r="H18" t="n">
         <v>46</v>
       </c>
     </row>
@@ -996,17 +974,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>82</v>
+      </c>
       <c r="E19" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F19" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G19" t="n">
-        <v>85</v>
-      </c>
-      <c r="H19" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1026,17 +1003,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>66</v>
+      </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G20" t="n">
-        <v>64</v>
-      </c>
-      <c r="H20" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1056,17 +1032,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>73</v>
+      </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F21" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G21" t="n">
-        <v>71</v>
-      </c>
-      <c r="H21" t="n">
         <v>74</v>
       </c>
     </row>
@@ -1076,27 +1051,26 @@
           <t>S021</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Caleb Bett</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Caleb Bett</t>
-        </is>
+      <c r="D22" t="n">
+        <v>90</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F22" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G22" t="n">
-        <v>88</v>
-      </c>
-      <c r="H22" t="n">
         <v>87</v>
       </c>
     </row>
@@ -1116,17 +1090,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>52</v>
+      </c>
       <c r="E23" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F23" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G23" t="n">
-        <v>54</v>
-      </c>
-      <c r="H23" t="n">
         <v>61</v>
       </c>
     </row>
@@ -1146,17 +1119,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>81</v>
+      </c>
       <c r="E24" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G24" t="n">
-        <v>80</v>
-      </c>
-      <c r="H24" t="n">
         <v>85</v>
       </c>
     </row>
@@ -1176,17 +1148,16 @@
           <t>Nairobi High School</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>60</v>
+      </c>
       <c r="E25" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F25" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G25" t="n">
-        <v>62</v>
-      </c>
-      <c r="H25" t="n">
         <v>58</v>
       </c>
     </row>
@@ -1206,17 +1177,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>88</v>
+      </c>
       <c r="E26" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F26" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G26" t="n">
-        <v>78</v>
-      </c>
-      <c r="H26" t="n">
         <v>85</v>
       </c>
     </row>
@@ -1236,17 +1206,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>55</v>
+      </c>
       <c r="E27" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
-      </c>
-      <c r="H27" t="n">
         <v>67</v>
       </c>
     </row>
@@ -1266,17 +1235,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>91</v>
+      </c>
       <c r="E28" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F28" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G28" t="n">
-        <v>88</v>
-      </c>
-      <c r="H28" t="n">
         <v>92</v>
       </c>
     </row>
@@ -1296,17 +1264,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>72</v>
+      </c>
       <c r="E29" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F29" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G29" t="n">
-        <v>80</v>
-      </c>
-      <c r="H29" t="n">
         <v>69</v>
       </c>
     </row>
@@ -1326,17 +1293,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>64</v>
+      </c>
       <c r="E30" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F30" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="G30" t="n">
-        <v>71</v>
-      </c>
-      <c r="H30" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1356,17 +1322,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>83</v>
+      </c>
       <c r="E31" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F31" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G31" t="n">
-        <v>79</v>
-      </c>
-      <c r="H31" t="n">
         <v>88</v>
       </c>
     </row>
@@ -1386,17 +1351,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>49</v>
+      </c>
       <c r="E32" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F32" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G32" t="n">
-        <v>52</v>
-      </c>
-      <c r="H32" t="n">
         <v>46</v>
       </c>
     </row>
@@ -1416,17 +1380,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>77</v>
+      </c>
       <c r="E33" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F33" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G33" t="n">
-        <v>74</v>
-      </c>
-      <c r="H33" t="n">
         <v>85</v>
       </c>
     </row>
@@ -1446,17 +1409,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>95</v>
+      </c>
       <c r="E34" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F34" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G34" t="n">
-        <v>89</v>
-      </c>
-      <c r="H34" t="n">
         <v>96</v>
       </c>
     </row>
@@ -1476,17 +1438,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>68</v>
+      </c>
       <c r="E35" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F35" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G35" t="n">
-        <v>65</v>
-      </c>
-      <c r="H35" t="n">
         <v>72</v>
       </c>
     </row>
@@ -1506,17 +1467,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>58</v>
+      </c>
       <c r="E36" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F36" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
-      </c>
-      <c r="H36" t="n">
         <v>54</v>
       </c>
     </row>
@@ -1536,17 +1496,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>86</v>
+      </c>
       <c r="E37" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F37" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G37" t="n">
-        <v>91</v>
-      </c>
-      <c r="H37" t="n">
         <v>89</v>
       </c>
     </row>
@@ -1566,17 +1525,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>73</v>
+      </c>
       <c r="E38" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F38" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G38" t="n">
-        <v>75</v>
-      </c>
-      <c r="H38" t="n">
         <v>81</v>
       </c>
     </row>
@@ -1596,17 +1554,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>42</v>
+      </c>
       <c r="E39" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F39" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G39" t="n">
-        <v>47</v>
-      </c>
-      <c r="H39" t="n">
         <v>45</v>
       </c>
     </row>
@@ -1626,17 +1583,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>80</v>
+      </c>
       <c r="E40" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F40" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G40" t="n">
-        <v>85</v>
-      </c>
-      <c r="H40" t="n">
         <v>78</v>
       </c>
     </row>
@@ -1656,17 +1612,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>69</v>
+      </c>
       <c r="E41" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F41" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G41" t="n">
-        <v>71</v>
-      </c>
-      <c r="H41" t="n">
         <v>66</v>
       </c>
     </row>
@@ -1686,17 +1641,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>92</v>
+      </c>
       <c r="E42" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F42" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G42" t="n">
-        <v>94</v>
-      </c>
-      <c r="H42" t="n">
         <v>90</v>
       </c>
     </row>
@@ -1716,17 +1670,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>61</v>
+      </c>
       <c r="E43" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F43" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G43" t="n">
-        <v>64</v>
-      </c>
-      <c r="H43" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1746,17 +1699,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>75</v>
+      </c>
       <c r="E44" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F44" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G44" t="n">
-        <v>72</v>
-      </c>
-      <c r="H44" t="n">
         <v>83</v>
       </c>
     </row>
@@ -1776,17 +1728,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>84</v>
+      </c>
       <c r="E45" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F45" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G45" t="n">
-        <v>81</v>
-      </c>
-      <c r="H45" t="n">
         <v>87</v>
       </c>
     </row>
@@ -1806,17 +1757,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>53</v>
+      </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F46" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G46" t="n">
-        <v>55</v>
-      </c>
-      <c r="H46" t="n">
         <v>51</v>
       </c>
     </row>
@@ -1836,17 +1786,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>79</v>
+      </c>
       <c r="E47" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F47" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G47" t="n">
-        <v>80</v>
-      </c>
-      <c r="H47" t="n">
         <v>82</v>
       </c>
     </row>
@@ -1866,17 +1815,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>87</v>
+      </c>
       <c r="E48" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F48" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G48" t="n">
-        <v>86</v>
-      </c>
-      <c r="H48" t="n">
         <v>91</v>
       </c>
     </row>
@@ -1896,17 +1844,16 @@
           <t>Alliance High School</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>66</v>
+      </c>
       <c r="E49" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F49" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G49" t="n">
-        <v>70</v>
-      </c>
-      <c r="H49" t="n">
         <v>64</v>
       </c>
     </row>
@@ -1926,17 +1873,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>85</v>
+      </c>
       <c r="E50" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F50" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G50" t="n">
-        <v>80</v>
-      </c>
-      <c r="H50" t="n">
         <v>88</v>
       </c>
     </row>
@@ -1956,17 +1902,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>68</v>
+      </c>
       <c r="E51" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F51" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G51" t="n">
-        <v>65</v>
-      </c>
-      <c r="H51" t="n">
         <v>72</v>
       </c>
     </row>
@@ -1986,17 +1931,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>91</v>
+      </c>
       <c r="E52" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F52" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G52" t="n">
-        <v>86</v>
-      </c>
-      <c r="H52" t="n">
         <v>89</v>
       </c>
     </row>
@@ -2016,17 +1960,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>54</v>
+      </c>
       <c r="E53" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F53" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G53" t="n">
-        <v>58</v>
-      </c>
-      <c r="H53" t="n">
         <v>63</v>
       </c>
     </row>
@@ -2046,17 +1989,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>77</v>
+      </c>
       <c r="E54" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F54" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G54" t="n">
-        <v>79</v>
-      </c>
-      <c r="H54" t="n">
         <v>85</v>
       </c>
     </row>
@@ -2076,17 +2018,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>63</v>
+      </c>
       <c r="E55" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F55" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G55" t="n">
-        <v>67</v>
-      </c>
-      <c r="H55" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2106,17 +2047,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>48</v>
+      </c>
       <c r="E56" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G56" t="n">
-        <v>50</v>
-      </c>
-      <c r="H56" t="n">
         <v>47</v>
       </c>
     </row>
@@ -2136,17 +2076,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>89</v>
+      </c>
       <c r="E57" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F57" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G57" t="n">
-        <v>88</v>
-      </c>
-      <c r="H57" t="n">
         <v>91</v>
       </c>
     </row>
@@ -2166,17 +2105,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>73</v>
+      </c>
       <c r="E58" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F58" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G58" t="n">
-        <v>71</v>
-      </c>
-      <c r="H58" t="n">
         <v>78</v>
       </c>
     </row>
@@ -2196,17 +2134,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="n">
+        <v>66</v>
+      </c>
       <c r="E59" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F59" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G59" t="n">
-        <v>64</v>
-      </c>
-      <c r="H59" t="n">
         <v>62</v>
       </c>
     </row>
@@ -2226,17 +2163,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>82</v>
+      </c>
       <c r="E60" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F60" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G60" t="n">
-        <v>80</v>
-      </c>
-      <c r="H60" t="n">
         <v>84</v>
       </c>
     </row>
@@ -2256,17 +2192,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="n">
+        <v>59</v>
+      </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F61" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G61" t="n">
-        <v>60</v>
-      </c>
-      <c r="H61" t="n">
         <v>55</v>
       </c>
     </row>
@@ -2286,17 +2221,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>70</v>
+      </c>
       <c r="E62" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F62" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G62" t="n">
-        <v>72</v>
-      </c>
-      <c r="H62" t="n">
         <v>69</v>
       </c>
     </row>
@@ -2316,17 +2250,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="n">
+        <v>42</v>
+      </c>
       <c r="E63" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F63" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G63" t="n">
-        <v>45</v>
-      </c>
-      <c r="H63" t="n">
         <v>51</v>
       </c>
     </row>
@@ -2346,17 +2279,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="n">
+        <v>94</v>
+      </c>
       <c r="E64" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F64" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G64" t="n">
-        <v>90</v>
-      </c>
-      <c r="H64" t="n">
         <v>93</v>
       </c>
     </row>
@@ -2376,17 +2308,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="n">
+        <v>79</v>
+      </c>
       <c r="E65" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F65" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G65" t="n">
-        <v>81</v>
-      </c>
-      <c r="H65" t="n">
         <v>80</v>
       </c>
     </row>
@@ -2406,17 +2337,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="n">
+        <v>61</v>
+      </c>
       <c r="E66" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F66" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G66" t="n">
-        <v>63</v>
-      </c>
-      <c r="H66" t="n">
         <v>58</v>
       </c>
     </row>
@@ -2436,17 +2366,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="n">
+        <v>86</v>
+      </c>
       <c r="E67" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F67" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G67" t="n">
-        <v>87</v>
-      </c>
-      <c r="H67" t="n">
         <v>89</v>
       </c>
     </row>
@@ -2466,17 +2395,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="n">
+        <v>67</v>
+      </c>
       <c r="E68" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F68" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G68" t="n">
-        <v>69</v>
-      </c>
-      <c r="H68" t="n">
         <v>70</v>
       </c>
     </row>
@@ -2496,17 +2424,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="n">
+        <v>52</v>
+      </c>
       <c r="E69" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F69" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G69" t="n">
-        <v>53</v>
-      </c>
-      <c r="H69" t="n">
         <v>49</v>
       </c>
     </row>
@@ -2526,17 +2453,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="n">
+        <v>80</v>
+      </c>
       <c r="E70" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F70" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G70" t="n">
-        <v>83</v>
-      </c>
-      <c r="H70" t="n">
         <v>82</v>
       </c>
     </row>
@@ -2556,17 +2482,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="n">
+        <v>75</v>
+      </c>
       <c r="E71" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F71" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G71" t="n">
-        <v>74</v>
-      </c>
-      <c r="H71" t="n">
         <v>76</v>
       </c>
     </row>
@@ -2586,17 +2511,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="n">
+        <v>90</v>
+      </c>
       <c r="E72" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F72" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G72" t="n">
-        <v>89</v>
-      </c>
-      <c r="H72" t="n">
         <v>92</v>
       </c>
     </row>
@@ -2616,17 +2540,16 @@
           <t>Tambach High School</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="n">
+        <v>58</v>
+      </c>
       <c r="E73" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F73" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G73" t="n">
-        <v>61</v>
-      </c>
-      <c r="H73" t="n">
         <v>57</v>
       </c>
     </row>
@@ -2646,17 +2569,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="n">
+        <v>89</v>
+      </c>
       <c r="E74" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F74" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G74" t="n">
-        <v>87</v>
-      </c>
-      <c r="H74" t="n">
         <v>93</v>
       </c>
     </row>
@@ -2676,17 +2598,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="n">
+        <v>60</v>
+      </c>
       <c r="E75" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F75" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G75" t="n">
-        <v>62</v>
-      </c>
-      <c r="H75" t="n">
         <v>58</v>
       </c>
     </row>
@@ -2706,17 +2627,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="n">
+        <v>84</v>
+      </c>
       <c r="E76" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F76" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G76" t="n">
-        <v>85</v>
-      </c>
-      <c r="H76" t="n">
         <v>82</v>
       </c>
     </row>
@@ -2736,17 +2656,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="n">
+        <v>73</v>
+      </c>
       <c r="E77" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F77" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G77" t="n">
-        <v>71</v>
-      </c>
-      <c r="H77" t="n">
         <v>79</v>
       </c>
     </row>
@@ -2766,17 +2685,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="n">
+        <v>52</v>
+      </c>
       <c r="E78" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F78" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G78" t="n">
-        <v>55</v>
-      </c>
-      <c r="H78" t="n">
         <v>61</v>
       </c>
     </row>
@@ -2796,17 +2714,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="n">
+        <v>91</v>
+      </c>
       <c r="E79" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F79" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G79" t="n">
-        <v>94</v>
-      </c>
-      <c r="H79" t="n">
         <v>92</v>
       </c>
     </row>
@@ -2826,17 +2743,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="n">
+        <v>66</v>
+      </c>
       <c r="E80" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F80" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G80" t="n">
-        <v>68</v>
-      </c>
-      <c r="H80" t="n">
         <v>65</v>
       </c>
     </row>
@@ -2856,17 +2772,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="n">
+        <v>45</v>
+      </c>
       <c r="E81" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G81" t="n">
-        <v>48</v>
-      </c>
-      <c r="H81" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2886,17 +2801,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="n">
+        <v>82</v>
+      </c>
       <c r="E82" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F82" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G82" t="n">
-        <v>81</v>
-      </c>
-      <c r="H82" t="n">
         <v>87</v>
       </c>
     </row>
@@ -2916,17 +2830,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="n">
+        <v>70</v>
+      </c>
       <c r="E83" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F83" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G83" t="n">
-        <v>72</v>
-      </c>
-      <c r="H83" t="n">
         <v>69</v>
       </c>
     </row>
@@ -2946,17 +2859,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="n">
+        <v>58</v>
+      </c>
       <c r="E84" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F84" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G84" t="n">
-        <v>59</v>
-      </c>
-      <c r="H84" t="n">
         <v>56</v>
       </c>
     </row>
@@ -2976,17 +2888,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="n">
+        <v>95</v>
+      </c>
       <c r="E85" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F85" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G85" t="n">
-        <v>90</v>
-      </c>
-      <c r="H85" t="n">
         <v>96</v>
       </c>
     </row>
@@ -3006,17 +2917,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="n">
+        <v>77</v>
+      </c>
       <c r="E86" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F86" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G86" t="n">
-        <v>78</v>
-      </c>
-      <c r="H86" t="n">
         <v>83</v>
       </c>
     </row>
@@ -3036,17 +2946,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="n">
+        <v>63</v>
+      </c>
       <c r="E87" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F87" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G87" t="n">
-        <v>65</v>
-      </c>
-      <c r="H87" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3066,17 +2975,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="n">
+        <v>41</v>
+      </c>
       <c r="E88" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F88" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G88" t="n">
-        <v>44</v>
-      </c>
-      <c r="H88" t="n">
         <v>46</v>
       </c>
     </row>
@@ -3096,17 +3004,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="n">
+        <v>88</v>
+      </c>
       <c r="E89" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F89" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G89" t="n">
-        <v>89</v>
-      </c>
-      <c r="H89" t="n">
         <v>91</v>
       </c>
     </row>
@@ -3126,17 +3033,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="n">
+        <v>71</v>
+      </c>
       <c r="E90" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F90" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G90" t="n">
-        <v>73</v>
-      </c>
-      <c r="H90" t="n">
         <v>70</v>
       </c>
     </row>
@@ -3156,17 +3062,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>54</v>
+      </c>
       <c r="E91" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F91" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>60</v>
-      </c>
-      <c r="H91" t="n">
         <v>53</v>
       </c>
     </row>
@@ -3186,17 +3091,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>86</v>
+      </c>
       <c r="E92" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F92" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G92" t="n">
-        <v>88</v>
-      </c>
-      <c r="H92" t="n">
         <v>85</v>
       </c>
     </row>
@@ -3216,17 +3120,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="n">
+        <v>68</v>
+      </c>
       <c r="E93" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F93" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G93" t="n">
-        <v>70</v>
-      </c>
-      <c r="H93" t="n">
         <v>66</v>
       </c>
     </row>
@@ -3246,17 +3149,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="n">
+        <v>49</v>
+      </c>
       <c r="E94" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F94" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G94" t="n">
-        <v>51</v>
-      </c>
-      <c r="H94" t="n">
         <v>47</v>
       </c>
     </row>
@@ -3276,17 +3178,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="n">
+        <v>80</v>
+      </c>
       <c r="E95" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F95" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G95" t="n">
-        <v>82</v>
-      </c>
-      <c r="H95" t="n">
         <v>84</v>
       </c>
     </row>
@@ -3306,17 +3207,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="n">
+        <v>75</v>
+      </c>
       <c r="E96" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F96" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G96" t="n">
-        <v>76</v>
-      </c>
-      <c r="H96" t="n">
         <v>77</v>
       </c>
     </row>
@@ -3336,17 +3236,16 @@
           <t>Singo're Girls</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="n">
+        <v>93</v>
+      </c>
       <c r="E97" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F97" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G97" t="n">
-        <v>95</v>
-      </c>
-      <c r="H97" t="n">
         <v>89</v>
       </c>
     </row>
